--- a/file-io/xlsx/parser/test-corpus/parity/controls/control-dropdown.xlsx
+++ b/file-io/xlsx/parser/test-corpus/parity/controls/control-dropdown.xlsx
@@ -377,5 +377,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>